--- a/outputs/Mukaさん_ユーザー要望書.xlsx
+++ b/outputs/Mukaさん_ユーザー要望書.xlsx
@@ -663,10 +663,14 @@
           <t>１－１－1-全体的に（特に8番）答えを認識してもらえない</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>こちらの対応記録が確認できていないため、状況を再調査のうえ改めてご連絡します。※解答の判定は完全一致ではなく類似度62%以上で正解としていますが、1-1-1は1単語(Iなど)のみの解答のため音声認識が誤認識しやすい箇所です</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -3119,7 +3123,11 @@
           <t>１－５－サブパート2 すべてのイラストが違います。差し替えをお願いしたいです。in the kitchen から　from Tokyo.　または、イラストすべて削除</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>1-5-2のイラストを問題内容(～は東京の出身です)に合うものへ差し替えました</t>
+        </is>
+      </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3150,7 +3158,11 @@
           <t>１－４－サブパート１と２　Requirementの訂正をしたい。「主語は代名詞で答えること」と付け加えたい。</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>1-4-1と1-4-2のRequirementに「ただし主語はHe,Sheなどの代名詞で答えること」を追記しました</t>
+        </is>
+      </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3181,7 +3193,11 @@
           <t>１－６－サブパート１　soccoer fan なのにfrom Tokyo のイラストが出てきています。イラストの削除または、差し替えをお願いしたい。</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr"/>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>1-6-1のイラストを問題内容(soccer fan)に合うものへ差し替えました</t>
+        </is>
+      </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3247,7 +3263,11 @@
           <t>1－７－１－（５）と（６）　イラストが逆I dance なのに　play the guitar.こちらは訂正をお願いしたいです。</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr"/>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>1-7-1の(5)と(6)のイラストを正しい組み合わせに入れ替えました</t>
+        </is>
+      </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3349,7 +3369,11 @@
 とじかっこを”」”へ訂正したい。</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>1-9-1のRequirementのとじかっこを「」」に修正しました(「～は英語を話します。」)</t>
+        </is>
+      </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3380,7 +3404,11 @@
           <t>1-10-2 イラストがすべてHeのところShe になってる。すべてＨｅ へ差し替えしたい。</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr"/>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>1-10-2のイラストをすべてHeに差し替えました</t>
+        </is>
+      </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3412,7 +3440,11 @@
 、問題を変えるかしたい。どちらが簡単ですか？</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr"/>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>1-9-2(1)～(6)はイラストと問題が一致するよう修正しました(その後の修正依頼も反映し、問題文・解答を最新化しています)</t>
+        </is>
+      </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3445,7 +3477,11 @@
 また、主語は（He She などの）代名詞で答えることの文を追加したい。</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>1-11-1のRequirementを「「go shopping」または「eat breakfast」を使い、主語に合う文章を考えましょう。また、主語は(He、Sheなどの)代名詞で答えましょう。」へ変更しました</t>
+        </is>
+      </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3477,7 +3513,11 @@
 また、主語は（He She などの）代名詞で答えることの文を追加したい。</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>1-11-2のRequirementを修正しました(その後の修正依頼を反映し、現在は「イラストを見て、主語に合う文章を考えましょう。」の文言です)</t>
+        </is>
+      </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3508,7 +3548,11 @@
           <t>１－１２－subpart 1,2 主語は（He She などの）代名詞で答えることの文を追加したい。</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>1-12-1と1-12-2のRequirementに「主語は(He、Sheなどの)代名詞で答えましょう」を追記しました</t>
+        </is>
+      </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3609,7 +3653,11 @@
           <t>１-18- 1 -1 肯定文を否定文に言いかえましょう。ただし主語はShe He などの代名詞に変えること。変更したい。</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr"/>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>1-18-1-1のRequirementを「肯定文を否定文に言いかえましょう。ただし主語はShe Heなどの代名詞に変えること。」へ変更しました</t>
+        </is>
+      </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3640,7 +3688,11 @@
           <t>1-20-2-1肯定文を否定文に言いかえましょう。主語はShe He などの代名詞で答えること。へ変更したい</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>1-20-2-1のRequirementを「肯定文を否定文に言いかえましょう。主語はShe Heなどの代名詞で答えること。」へ変更しました</t>
+        </is>
+      </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3671,13 +3723,21 @@
           <t>ログイン画面でログインボタンを押すと、ボタンの色が変わる、または音が出る使用に出来ますか？反応がまだ遅く、反応しているの分からず何度もボタンを押してしまう。</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr"/>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>LOGINボタンを押すと「Logging in...」表示に切り替わり、処理中は再度押せないようにしました。5秒以上かかる場合は「サーバー起動中です」の案内も表示されます</t>
+        </is>
+      </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="57" customHeight="1">
       <c r="A89" s="7" t="n">
@@ -3698,13 +3758,21 @@
           <t>長い間ログインしていないと、認証が必要です。と画面に出ますが、再度リンクを探してログインし直すしか方法はないのでしょうか？ログインしなおしてください。など実際にしなければならないことを、書いてあったら分かりやすいかなと思います。</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr"/>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>認証切れの際のメッセージを「ログインの有効期限が切れています。再度ログインしてください」のように、実際に行うことが分かる文言に統一しました</t>
+        </is>
+      </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="49" customHeight="1">
       <c r="A90" s="4" t="n">
@@ -3725,13 +3793,21 @@
           <t>一日画面を開いたまま、次の日続きをしようとすると、ステージ画面のスタートを押してもゲームの続きができず、承認が必要です。と言われます。そこから承認画面にいくことが出来るようにすることは出来ますか？</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>原因はiPadのSafariが一定期間で認証情報(Cookie)を破棄する仕様でした。通信方式を変更してこの問題自体を解消しています。認証切れになった場合も「再度ログインしてください」と案内が表示されます</t>
+        </is>
+      </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" s="7" t="n">
@@ -3752,13 +3828,21 @@
           <t>3-8-1 の問題に3-8-２を付け足すことは可能でしょうか？また、今はイラストがない状態なのですが、今からイラストを足すことはできますか？</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>3-8-2を新設し、問題8問・解答・イラスト8枚を追加しました。イラストは1-24-1/1-25-1にも追加済みです。※現在はローカル環境での反映のため、ご確認後に本番へ反映します</t>
+        </is>
+      </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" s="4" t="n">
@@ -3779,13 +3863,21 @@
           <t>3-18-1-1 、3-19-1-1 … ～～2回読まれるはずの回答条件が、1度しか読まれませんでした。</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr"/>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>音声の取得に失敗した場合に自動で再取得するようにし、2回読み上げが欠けないようにしました(No146と同じ対応)</t>
+        </is>
+      </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" s="7" t="n">
@@ -3806,13 +3898,21 @@
           <t>3-23-2-1~8 問題文が7番までしか読まれませんでした。</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr"/>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>音声取得失敗時の自動再取得(No146と同じ対応)に加え、完成版データで3-23-2の全8問が正しく出題されることを自動チェックで確認しました</t>
+        </is>
+      </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3911,7 +4011,11 @@
           <t>ログインに1分ほどかかってしまうのですが、１，２秒でログインすることは難しいでしょうか？</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>データと音声のキャッシュを導入し、2回目以降のログイン・読み込みを高速化しました。初回アクセスの待ち時間はNo136でサーバーの事前起動を追加しています(完全な解消にはサーバープランの変更が必要なため、納品時にご相談します)</t>
+        </is>
+      </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -3943,7 +4047,11 @@
 ０．５秒ほど短くできますか？</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>正解表示(回答文と絵)が消えるまでの時間を約0.5秒短縮しました</t>
+        </is>
+      </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -4009,7 +4117,11 @@
           <t>327: 1-21-1-4 read が過去形読みになる。問題を変えるしかないですか？</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>readを現在形(リード)で発音するよう音声合成に発音指定を追加し、古い音声キャッシュも無効化しました(No138/142と同じ対応)。問題文の変更は不要です</t>
+        </is>
+      </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -4017,7 +4129,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4152,11 @@
           <t>1-23-2-6 イラストが表示されませんでした。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>イラストのファイル名の誤記(1_23_2_0.6png → 1_23_2_06.png)が原因でした。修正して表示されることを確認しました</t>
+        </is>
+      </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
           <t>完了</t>
@@ -4048,7 +4164,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
